--- a/DXLibProject_Start/Data/CSV/PlayerEmissiveColor.xlsx
+++ b/DXLibProject_Start/Data/CSV/PlayerEmissiveColor.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student1\Desktop\2nd_3DAction\DXLibProject_Start\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student1\Desktop\2nd_3DAction\DXLibProject_Start\Data\CSV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EB904D3-7612-4FB7-B5EC-0AF80B5ABCBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{035BA3B2-B326-4FDF-91AC-2605F8771A7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1470" yWindow="1470" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -390,13 +390,13 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="B2">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="C2">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="D2">
         <v>1</v>

--- a/DXLibProject_Start/Data/CSV/PlayerEmissiveColor.xlsx
+++ b/DXLibProject_Start/Data/CSV/PlayerEmissiveColor.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student1\Desktop\2nd_3DAction\DXLibProject_Start\Data\CSV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{035BA3B2-B326-4FDF-91AC-2605F8771A7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E994ABEC-4AF6-47F7-BD86-2D98827B5C91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -30,19 +30,19 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
-    <t>Red</t>
+    <t>red</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>Green</t>
+    <t>green</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>Blue</t>
+    <t>blue</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>Alpha</t>
+    <t>alpha</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
